--- a/Notes/Function notes.xlsx
+++ b/Notes/Function notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Envision\Cursor\stockmanagement\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7703110-C625-4708-9BFE-AA3677B01B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFB81EE-E00E-4785-BC01-0E4697741643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19290" windowHeight="11010" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Inklomste vir Belasting 2025" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="96">
   <si>
     <t>Capri</t>
   </si>
@@ -288,6 +288,48 @@
   <si>
     <t>qty</t>
   </si>
+  <si>
+    <t>SYR208</t>
+  </si>
+  <si>
+    <t>COC245</t>
+  </si>
+  <si>
+    <t>SAL967</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>TOTALE VOLUME IN</t>
+  </si>
+  <si>
+    <t>TOTALE VOLUME UIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verander al die </t>
+  </si>
+  <si>
+    <t>pr_booking_out_all</t>
+  </si>
+  <si>
+    <t>pr_booking_out_by_stock_code</t>
+  </si>
+  <si>
+    <t>pr_booking_out_last_three_months</t>
+  </si>
+  <si>
+    <t>Sit Unit Price by popup</t>
+  </si>
+  <si>
+    <t>Hide Stock Item ID in popup</t>
+  </si>
+  <si>
+    <t>Wys View knoppies altyd</t>
+  </si>
 </sst>
 </file>
 
@@ -296,7 +338,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +358,13 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -360,7 +409,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,6 +420,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -456,11 +510,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -474,12 +529,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -493,15 +548,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -513,15 +568,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -48102,7 +48167,7 @@
       <c r="M2" s="17">
         <v>46105</v>
       </c>
-      <c r="N2" s="34">
+      <c r="N2" s="35">
         <v>6000</v>
       </c>
     </row>
@@ -48132,7 +48197,7 @@
       <c r="M3" s="17">
         <v>46113</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="35">
         <v>5000</v>
       </c>
     </row>
@@ -48161,7 +48226,7 @@
       <c r="M4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="35">
         <v>11000</v>
       </c>
     </row>
@@ -48192,7 +48257,7 @@
       <c r="M5" s="17">
         <v>46176</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="35">
         <v>10450</v>
       </c>
     </row>
@@ -48217,7 +48282,7 @@
       <c r="M6" s="19">
         <v>46192</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="35">
         <v>10000</v>
       </c>
     </row>
@@ -48248,7 +48313,7 @@
       <c r="M7" s="17">
         <v>46198</v>
       </c>
-      <c r="N7" s="34">
+      <c r="N7" s="35">
         <v>10000</v>
       </c>
     </row>
@@ -48267,7 +48332,7 @@
       <c r="M8" s="19">
         <v>46226</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="35">
         <v>10000</v>
       </c>
     </row>
@@ -48284,7 +48349,7 @@
       <c r="J9" s="3"/>
       <c r="K9" s="5"/>
       <c r="M9" s="17"/>
-      <c r="N9" s="35"/>
+      <c r="N9" s="36"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D10" s="17">
@@ -48303,13 +48368,13 @@
       <c r="J10" s="3"/>
       <c r="K10" s="5"/>
       <c r="M10" s="17"/>
-      <c r="N10" s="34"/>
+      <c r="N10" s="35"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D11" s="19">
         <v>46226</v>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <v>10000</v>
       </c>
       <c r="F11" s="5"/>
@@ -48318,7 +48383,7 @@
       <c r="J11" s="3"/>
       <c r="K11" s="5"/>
       <c r="M11" s="17"/>
-      <c r="N11" s="35"/>
+      <c r="N11" s="36"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D12" s="17"/>
@@ -48329,7 +48394,7 @@
       <c r="J12" s="3"/>
       <c r="K12" s="5"/>
       <c r="M12" s="17"/>
-      <c r="N12" s="34"/>
+      <c r="N12" s="35"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="D13" s="17"/>
@@ -48340,12 +48405,24 @@
       <c r="J13" s="3"/>
       <c r="K13" s="5"/>
       <c r="M13" s="17"/>
-      <c r="N13" s="34"/>
+      <c r="N13" s="35"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E14" s="21">
         <f>SUM(E2:E13)</f>
         <v>62450</v>
+      </c>
+      <c r="F14" s="21">
+        <f>SUM(F10:F13)</f>
+        <v>14200</v>
+      </c>
+      <c r="G14" s="21">
+        <f>SUM(E14:F14)</f>
+        <v>76650</v>
+      </c>
+      <c r="H14" s="21">
+        <f>SUM(E14:G14)</f>
+        <v>153300</v>
       </c>
       <c r="K14" s="6">
         <f>SUM(K2:K13)</f>
@@ -48379,13 +48456,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4750D6-39CA-4555-B7BD-12504A33D1C5}">
-  <dimension ref="B1:O26"/>
+  <dimension ref="B1:P43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" width="37" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="8" max="8" width="61" customWidth="1"/>
     <col min="9" max="9" width="15.81640625" customWidth="1"/>
     <col min="10" max="10" width="18.453125" customWidth="1"/>
+    <col min="15" max="15" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.35">
@@ -48657,7 +48736,7 @@
       <c r="J16" s="28"/>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" spans="7:11" ht="16" x14ac:dyDescent="0.4">
+    <row r="17" spans="7:16" ht="16" x14ac:dyDescent="0.4">
       <c r="G17" s="27" t="s">
         <v>56</v>
       </c>
@@ -48670,14 +48749,14 @@
       <c r="J17" s="25"/>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" spans="7:11" ht="16" x14ac:dyDescent="0.4">
+    <row r="18" spans="7:16" ht="16" x14ac:dyDescent="0.4">
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="I18" s="25"/>
       <c r="J18" s="25"/>
       <c r="K18" s="25"/>
     </row>
-    <row r="19" spans="7:11" ht="16" x14ac:dyDescent="0.4">
+    <row r="19" spans="7:16" ht="16" x14ac:dyDescent="0.4">
       <c r="G19" s="27" t="s">
         <v>55</v>
       </c>
@@ -48694,7 +48773,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="7:11" ht="16" x14ac:dyDescent="0.4">
+    <row r="20" spans="7:16" ht="16" x14ac:dyDescent="0.4">
       <c r="G20" s="27" t="s">
         <v>57</v>
       </c>
@@ -48710,21 +48789,165 @@
       <c r="K20" s="26" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="P20" s="32"/>
+    </row>
+    <row r="21" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="O21" s="32">
+        <v>46238</v>
+      </c>
+      <c r="P21" s="32"/>
+    </row>
+    <row r="22" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" s="32">
+        <v>46245</v>
+      </c>
+      <c r="P22" s="32"/>
+    </row>
+    <row r="23" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23" s="32">
+        <v>46252</v>
+      </c>
+      <c r="P23" s="32"/>
+    </row>
+    <row r="24" spans="7:16" x14ac:dyDescent="0.35">
       <c r="G24" s="24" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24" s="32">
+        <v>46259</v>
+      </c>
+      <c r="P24" s="32"/>
+    </row>
+    <row r="25" spans="7:16" x14ac:dyDescent="0.35">
       <c r="G25" s="24" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="26" spans="7:11" x14ac:dyDescent="0.35">
+      <c r="N25">
+        <v>4</v>
+      </c>
+      <c r="O25" s="32">
+        <v>46266</v>
+      </c>
+      <c r="P25" s="32"/>
+    </row>
+    <row r="26" spans="7:16" x14ac:dyDescent="0.35">
       <c r="G26" t="s">
         <v>66</v>
       </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26" s="32">
+        <v>46273</v>
+      </c>
+      <c r="P26" s="32"/>
+    </row>
+    <row r="27" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" s="32">
+        <v>46280</v>
+      </c>
+      <c r="P27" s="32"/>
+    </row>
+    <row r="28" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="G28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="N28">
+        <v>2</v>
+      </c>
+      <c r="O28" s="32">
+        <v>46287</v>
+      </c>
+      <c r="P28" s="32"/>
+    </row>
+    <row r="29" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="H29" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="N29">
+        <v>3</v>
+      </c>
+      <c r="O29" s="32">
+        <v>46294</v>
+      </c>
+      <c r="P29" s="32"/>
+    </row>
+    <row r="30" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="H30" t="s">
+        <v>66</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30" s="32">
+        <v>46301</v>
+      </c>
+      <c r="P30" s="32"/>
+    </row>
+    <row r="31" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31" s="32">
+        <v>46308</v>
+      </c>
+      <c r="P31" s="32"/>
+    </row>
+    <row r="32" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="H32" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="P32" s="32"/>
+    </row>
+    <row r="33" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="H33" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="P33" s="32"/>
+    </row>
+    <row r="34" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="H34" t="s">
+        <v>92</v>
+      </c>
+      <c r="P34" s="32"/>
+    </row>
+    <row r="35" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="P35" s="32"/>
+    </row>
+    <row r="36" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="G36" t="s">
+        <v>95</v>
+      </c>
+      <c r="P36" s="32"/>
+    </row>
+    <row r="37" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="G37" t="s">
+        <v>93</v>
+      </c>
+      <c r="P37" s="32"/>
+    </row>
+    <row r="38" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="G38" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="43" spans="7:16" x14ac:dyDescent="0.35">
+      <c r="P43" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -48797,7 +49020,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="12">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -48824,7 +49047,7 @@
       <c r="A6" s="11"/>
       <c r="B6" s="12">
         <f>SUM(B1:B5)</f>
-        <v>42500</v>
+        <v>38500</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -49143,7 +49366,7 @@
       <c r="A32" s="15"/>
       <c r="B32" s="15">
         <f>B6-F32</f>
-        <v>-5996</v>
+        <v>-9996</v>
       </c>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -49160,19 +49383,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C21136-C2F8-41B1-9BF0-1E816375C2F6}">
-  <dimension ref="C1:K15"/>
+  <dimension ref="B1:Q34"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="7" max="7" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C2" t="s">
         <v>68</v>
       </c>
@@ -49183,7 +49406,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>69</v>
       </c>
@@ -49194,7 +49417,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C4" s="2">
         <v>6100</v>
       </c>
@@ -49205,7 +49428,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>70</v>
       </c>
@@ -49216,7 +49439,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>71</v>
       </c>
@@ -49227,7 +49450,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.35">
       <c r="G7" t="s">
         <v>71</v>
       </c>
@@ -49235,12 +49458,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C12" s="8" t="s">
         <v>79</v>
       </c>
@@ -49254,43 +49477,262 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C13" s="32">
+    <row r="13" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C13" s="33">
         <v>4</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <v>46388</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <v>3</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="34">
         <v>46357</v>
       </c>
     </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C14" s="32">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C14" s="33">
         <v>17</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <v>46357</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <v>8</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="34">
         <v>46327</v>
       </c>
     </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.35">
-      <c r="C15" s="32">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C15" s="33">
         <v>8</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="34">
         <v>46327</v>
       </c>
+      <c r="O15">
+        <v>90</v>
+      </c>
+      <c r="P15">
+        <v>90</v>
+      </c>
+      <c r="Q15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="E18" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="37"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4.8194999999999997</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.754</v>
+      </c>
+      <c r="H19">
+        <f>C19-F19</f>
+        <v>2.0654999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.573</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1.573</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ref="H20:H21" si="0">C20-F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1.0399999999999999E-3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.0399999999999999E-3</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="37"/>
+      <c r="E26" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="3">
+        <v>133</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="3">
+        <v>35</v>
+      </c>
+      <c r="H27">
+        <f>C27-F27</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="3">
+        <v>51</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f t="shared" ref="H28:H29" si="1">C28-F28</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="3">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="39"/>
+      <c r="E31" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="39"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="40">
+        <f>C19*C27</f>
+        <v>640.99349999999993</v>
+      </c>
+      <c r="E32" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="40">
+        <f>F19*F27</f>
+        <v>96.39</v>
+      </c>
+      <c r="H32">
+        <f>C32-F32</f>
+        <v>544.60349999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="40">
+        <f t="shared" ref="C33:C34" si="2">C20*C28</f>
+        <v>80.222999999999999</v>
+      </c>
+      <c r="E33" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" s="40">
+        <f t="shared" ref="F33:F34" si="3">F20*F28</f>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f t="shared" ref="H33:H34" si="4">C33-F33</f>
+        <v>80.222999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="40">
+        <f t="shared" si="2"/>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="40">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="4"/>
+        <v>2.5999999999999999E-2</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="E31:F31"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Notes/Function notes.xlsx
+++ b/Notes/Function notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Envision\Cursor\stockmanagement\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA458BB-A55D-4034-8B8E-058F83A60D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8645B6-72A1-4509-8CB2-06F2FC1CA762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
   </bookViews>
@@ -20,7 +20,6 @@
     <sheet name="Sheet2" sheetId="10" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="100">
   <si>
     <t>Capri</t>
   </si>
@@ -92,9 +91,6 @@
   </si>
   <si>
     <t>MTN</t>
-  </si>
-  <si>
-    <t>Huisversekering</t>
   </si>
   <si>
     <t>Kerk</t>
@@ -324,6 +320,27 @@
   <si>
     <t>Wys View knoppies altyd</t>
   </si>
+  <si>
+    <t>CM25615</t>
+  </si>
+  <si>
+    <t>ACL18602</t>
+  </si>
+  <si>
+    <t>SPAAR</t>
+  </si>
+  <si>
+    <t>Spaargeld</t>
+  </si>
+  <si>
+    <t>Gebruik</t>
+  </si>
+  <si>
+    <t>Maande</t>
+  </si>
+  <si>
+    <t>Siyanda</t>
+  </si>
 </sst>
 </file>
 
@@ -451,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -515,13 +532,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -565,6 +595,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -574,23 +614,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -48115,10 +48152,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19813495-76F4-44A6-86F1-2EF0E8BEAE30}">
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.90625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" style="18" customWidth="1"/>
+    <col min="5" max="7" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.7265625" style="10" customWidth="1"/>
     <col min="10" max="10" width="15.26953125" customWidth="1"/>
     <col min="11" max="11" width="12.453125" style="2" customWidth="1"/>
@@ -48127,7 +48165,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="16">
-      <c r="D1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="44" t="s">
+        <v>99</v>
+      </c>
       <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
@@ -48137,37 +48178,38 @@
       <c r="G1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="M1" s="30" t="s">
+      <c r="I1" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="31"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="M1" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="N1" s="39"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
     </row>
     <row r="2" spans="1:19" ht="16">
       <c r="A2">
         <v>59480</v>
       </c>
-      <c r="D2" s="17">
+      <c r="C2" s="17">
         <v>46105</v>
       </c>
-      <c r="E2" s="5">
+      <c r="D2" s="3"/>
+      <c r="E2" s="45">
         <v>6000</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
       <c r="I2" s="19">
         <v>46090</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" s="5">
+        <v>38</v>
+      </c>
+      <c r="K2" s="32">
         <v>11000</v>
       </c>
       <c r="L2">
@@ -48177,356 +48219,509 @@
       <c r="M2" s="17">
         <v>46105</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="32">
         <v>6000</v>
       </c>
-      <c r="R2" s="42"/>
-      <c r="S2" s="41"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="34"/>
     </row>
     <row r="3" spans="1:19" ht="16">
-      <c r="D3" s="17">
+      <c r="C3" s="17">
         <v>46106</v>
       </c>
-      <c r="F3" s="5">
+      <c r="D3" s="3"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="32">
         <v>44400</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="32">
         <v>17500</v>
       </c>
       <c r="I3" s="19">
         <v>46119</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="5">
+        <v>39</v>
+      </c>
+      <c r="K3" s="32">
         <v>21450</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L7" si="0">K3/550</f>
+        <f t="shared" ref="L3" si="0">K3/550</f>
         <v>39</v>
       </c>
       <c r="M3" s="17">
         <v>46113</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="32">
         <v>5000</v>
       </c>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
     </row>
     <row r="4" spans="1:19" ht="16">
-      <c r="D4" s="17">
+      <c r="C4" s="17">
         <v>46113</v>
       </c>
-      <c r="E4" s="5">
+      <c r="D4" s="3"/>
+      <c r="E4" s="45">
         <v>5000</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
       <c r="I4" s="19">
         <v>46170</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="5">
+        <v>40</v>
+      </c>
+      <c r="K4" s="32">
         <v>37400</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="N4" s="40">
+        <v>29</v>
+      </c>
+      <c r="N4" s="32">
         <v>11000</v>
       </c>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
     </row>
     <row r="5" spans="1:19" ht="16">
-      <c r="D5" s="17">
+      <c r="C5" s="17">
         <v>46136</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5">
+      <c r="D5" s="3"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="32">
         <v>42800</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="32">
         <v>17500</v>
       </c>
       <c r="I5" s="19">
         <v>46192</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="5">
+        <v>43</v>
+      </c>
+      <c r="K5" s="32">
         <v>9800</v>
       </c>
       <c r="L5">
-        <f>K4/550</f>
-        <v>68</v>
+        <f>K5/550</f>
+        <v>17.818181818181817</v>
       </c>
       <c r="M5" s="17">
         <v>46176</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="32">
         <v>10450</v>
       </c>
-      <c r="R5" s="41"/>
-      <c r="S5" s="41"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
     </row>
     <row r="6" spans="1:19" ht="16">
-      <c r="D6" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="5">
+      <c r="C6" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="45">
         <v>11000</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
       <c r="I6" s="19">
         <v>46203</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="5">
+        <v>45</v>
+      </c>
+      <c r="K6" s="32">
         <v>21450</v>
       </c>
       <c r="M6" s="19">
         <v>46192</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="32">
         <v>10000</v>
       </c>
-      <c r="R6" s="41"/>
-      <c r="S6" s="41"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
     </row>
     <row r="7" spans="1:19" ht="16">
-      <c r="D7" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5">
+      <c r="C7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="32">
         <v>42800</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="32">
         <v>17500</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="5"/>
+      <c r="I7" s="19">
+        <v>46231</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" s="32">
+        <v>18700</v>
+      </c>
       <c r="L7">
-        <f>K6/550</f>
-        <v>39</v>
+        <f>K7/550</f>
+        <v>34</v>
       </c>
       <c r="M7" s="17">
         <v>46198</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="32">
         <v>10000</v>
       </c>
-      <c r="R7" s="41"/>
-      <c r="S7" s="41"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
     </row>
     <row r="8" spans="1:19" ht="16">
-      <c r="D8" s="17">
+      <c r="C8" s="17">
         <v>46176</v>
       </c>
-      <c r="E8" s="5">
+      <c r="D8" s="3"/>
+      <c r="E8" s="45">
         <v>10450</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="5"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="I8" s="19">
+        <v>46234</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="32">
+        <v>291.5</v>
+      </c>
       <c r="M8" s="19">
         <v>46226</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="32">
         <v>10000</v>
       </c>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
     </row>
     <row r="9" spans="1:19" ht="16">
-      <c r="D9" s="19">
+      <c r="C9" s="19">
         <v>46192</v>
       </c>
-      <c r="E9" s="5">
+      <c r="D9" s="3"/>
+      <c r="E9" s="45">
         <v>10000</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="I9" s="20"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="5"/>
+      <c r="K9" s="32"/>
       <c r="M9" s="17">
         <v>46230</v>
       </c>
-      <c r="N9" s="40">
+      <c r="N9" s="32">
         <v>7400</v>
       </c>
-      <c r="R9" s="41"/>
-      <c r="S9" s="41"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
     </row>
     <row r="10" spans="1:19" ht="16">
-      <c r="D10" s="17">
+      <c r="C10" s="17">
         <v>46198</v>
       </c>
-      <c r="E10" s="5">
+      <c r="D10" s="3"/>
+      <c r="E10" s="45">
         <v>10000</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="32">
         <v>14200</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="32">
         <v>17500</v>
       </c>
       <c r="I10" s="20"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="5"/>
+      <c r="K10" s="32"/>
       <c r="M10" s="17">
         <v>46230</v>
       </c>
-      <c r="N10" s="40">
+      <c r="N10" s="32">
         <v>9800</v>
       </c>
-      <c r="R10" s="41"/>
-      <c r="S10" s="41"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
     </row>
     <row r="11" spans="1:19" ht="16">
-      <c r="D11" s="19">
+      <c r="C11" s="19">
         <v>46226</v>
       </c>
-      <c r="E11" s="35">
+      <c r="D11" s="3"/>
+      <c r="E11" s="45">
         <v>10000</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
       <c r="I11" s="20"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="5"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="40"/>
-      <c r="R11" s="41"/>
-      <c r="S11" s="41"/>
+      <c r="K11" s="32"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="3"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
     </row>
     <row r="12" spans="1:19" ht="16">
-      <c r="D12" s="17">
+      <c r="C12" s="17">
         <v>46230</v>
       </c>
-      <c r="E12" s="40">
+      <c r="D12" s="3"/>
+      <c r="E12" s="45">
         <v>7400</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
       <c r="I12" s="20"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="5"/>
+      <c r="K12" s="32"/>
       <c r="M12" s="17"/>
-      <c r="N12" s="40"/>
-      <c r="R12" s="41"/>
-      <c r="S12" s="41"/>
+      <c r="N12" s="32"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
     </row>
     <row r="13" spans="1:19" ht="16">
-      <c r="D13" s="17">
+      <c r="C13" s="17">
         <v>46230</v>
       </c>
-      <c r="E13" s="40">
+      <c r="D13" s="3"/>
+      <c r="E13" s="45">
         <v>9800</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
       <c r="I13" s="20"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="5"/>
+      <c r="K13" s="32"/>
       <c r="M13" s="17"/>
-      <c r="N13" s="40"/>
-      <c r="R13" s="41"/>
-      <c r="S13" s="41"/>
+      <c r="N13" s="32"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
     </row>
     <row r="14" spans="1:19" ht="16">
-      <c r="D14" s="17">
+      <c r="C14" s="17">
         <v>46231</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3">
+      <c r="D14" s="3"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="32">
         <v>13800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="32">
         <v>17500</v>
       </c>
-      <c r="K14" s="6">
+      <c r="I14" s="20"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="5"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="3"/>
+      <c r="P14" s="2">
+        <f>K27-N27</f>
+        <v>40441.5</v>
+      </c>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+    </row>
+    <row r="15" spans="1:19" ht="16">
+      <c r="C15" s="17">
+        <v>46252</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="32">
+        <v>14000</v>
+      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="5"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="3"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+    </row>
+    <row r="16" spans="1:19" ht="16">
+      <c r="C16" s="17">
+        <v>46259</v>
+      </c>
+      <c r="D16" s="32">
+        <v>34650</v>
+      </c>
+      <c r="E16" s="45"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="5"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="3"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+    </row>
+    <row r="17" spans="3:14">
+      <c r="C17" s="17"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="5"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14">
+      <c r="C18" s="17"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="5"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14">
+      <c r="C19" s="17"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="5"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14">
+      <c r="C20" s="17"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="5"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14">
+      <c r="C21" s="17"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="5"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14">
+      <c r="C22" s="17"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="5"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14">
+      <c r="C23" s="17"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="5"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14">
+      <c r="C24" s="17"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="5"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14">
+      <c r="C25" s="17"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="5"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14">
+      <c r="C26" s="17"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="5"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14">
+      <c r="D27">
+        <f>SUM(D2:D26)</f>
+        <v>34650</v>
+      </c>
+      <c r="E27" s="21">
+        <f>SUM(E2:E16)</f>
+        <v>93650</v>
+      </c>
+      <c r="F27" s="21">
+        <f>SUM(F2:F16)</f>
+        <v>158000</v>
+      </c>
+      <c r="G27" s="21">
+        <f>SUM(G2:G16)</f>
+        <v>87500</v>
+      </c>
+      <c r="H27" s="21">
+        <f>SUM(D27:G27)</f>
+        <v>373800</v>
+      </c>
+      <c r="K27" s="43">
         <f>SUM(K2:K13)</f>
-        <v>101100</v>
-      </c>
-      <c r="M14" s="18"/>
-      <c r="N14" s="6">
+        <v>120091.5</v>
+      </c>
+      <c r="N27" s="42">
         <f>SUM(N2:N13)</f>
         <v>79650</v>
       </c>
-      <c r="P14" s="2">
-        <f>K14-N14</f>
-        <v>21450</v>
-      </c>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-    </row>
-    <row r="15" spans="1:19" ht="16">
-      <c r="D15" s="17"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-    </row>
-    <row r="16" spans="1:19" ht="16">
-      <c r="D16" s="17"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-    </row>
-    <row r="17" spans="5:19" ht="16">
-      <c r="R17" s="41"/>
-      <c r="S17" s="41"/>
-    </row>
-    <row r="18" spans="5:19" ht="16">
-      <c r="K18" s="5"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-    </row>
-    <row r="19" spans="5:19" ht="16">
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-    </row>
-    <row r="20" spans="5:19" ht="16">
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-    </row>
-    <row r="22" spans="5:19">
-      <c r="E22" s="21">
-        <f>SUM(E2:E13)</f>
-        <v>79650</v>
-      </c>
-      <c r="F22" s="21">
-        <f>SUM(F10:F13)</f>
-        <v>14200</v>
-      </c>
-      <c r="G22" s="21">
-        <f>SUM(E22:F22)</f>
-        <v>93850</v>
-      </c>
-      <c r="H22" s="21">
-        <f>SUM(E22:G22)</f>
-        <v>187700</v>
-      </c>
-    </row>
-    <row r="24" spans="5:19">
-      <c r="E24" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -48557,17 +48752,17 @@
       <c r="D1" s="22"/>
       <c r="E1" s="22"/>
       <c r="F1" s="22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="23" t="s">
         <v>47</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>48</v>
       </c>
       <c r="I1" s="23"/>
       <c r="J1" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K1" s="23"/>
       <c r="L1" s="23"/>
@@ -48590,7 +48785,7 @@
         <v>88</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J2" s="23">
         <v>100</v>
@@ -48614,7 +48809,7 @@
         <v>88</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J3" s="23">
         <v>50</v>
@@ -48809,26 +49004,26 @@
     </row>
     <row r="16" spans="2:15" ht="16">
       <c r="G16" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J16" s="28"/>
       <c r="K16" s="25"/>
     </row>
     <row r="17" spans="7:16" ht="16">
       <c r="G17" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H17" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I17" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J17" s="25"/>
       <c r="K17" s="25"/>
@@ -48842,196 +49037,196 @@
     </row>
     <row r="19" spans="7:16" ht="16">
       <c r="G19" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="I19" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="26" t="s">
-        <v>59</v>
-      </c>
       <c r="K19" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="7:16" ht="16">
       <c r="G20" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H20" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="I20" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="J20" s="26" t="s">
-        <v>59</v>
-      </c>
       <c r="K20" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="P20" s="32"/>
+        <v>60</v>
+      </c>
+      <c r="P20" s="29"/>
     </row>
     <row r="21" spans="7:16">
-      <c r="O21" s="32">
+      <c r="O21" s="29">
         <v>46238</v>
       </c>
-      <c r="P21" s="32"/>
+      <c r="P21" s="29"/>
     </row>
     <row r="22" spans="7:16">
       <c r="N22">
         <v>1</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="29">
         <v>46245</v>
       </c>
-      <c r="P22" s="32"/>
+      <c r="P22" s="29"/>
     </row>
     <row r="23" spans="7:16">
       <c r="N23">
         <v>2</v>
       </c>
-      <c r="O23" s="32">
+      <c r="O23" s="29">
         <v>46252</v>
       </c>
-      <c r="P23" s="32"/>
+      <c r="P23" s="29"/>
     </row>
     <row r="24" spans="7:16">
       <c r="G24" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N24">
         <v>3</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="29">
         <v>46259</v>
       </c>
-      <c r="P24" s="32"/>
+      <c r="P24" s="29"/>
     </row>
     <row r="25" spans="7:16">
       <c r="G25" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N25">
         <v>4</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="29">
         <v>46266</v>
       </c>
-      <c r="P25" s="32"/>
+      <c r="P25" s="29"/>
     </row>
     <row r="26" spans="7:16">
       <c r="G26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
-      <c r="O26" s="32">
+      <c r="O26" s="29">
         <v>46273</v>
       </c>
-      <c r="P26" s="32"/>
+      <c r="P26" s="29"/>
     </row>
     <row r="27" spans="7:16">
       <c r="N27">
         <v>1</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="29">
         <v>46280</v>
       </c>
-      <c r="P27" s="32"/>
+      <c r="P27" s="29"/>
     </row>
     <row r="28" spans="7:16">
       <c r="G28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N28">
         <v>2</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="29">
         <v>46287</v>
       </c>
-      <c r="P28" s="32"/>
+      <c r="P28" s="29"/>
     </row>
     <row r="29" spans="7:16">
       <c r="H29" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N29">
         <v>3</v>
       </c>
-      <c r="O29" s="32">
+      <c r="O29" s="29">
         <v>46294</v>
       </c>
-      <c r="P29" s="32"/>
+      <c r="P29" s="29"/>
     </row>
     <row r="30" spans="7:16">
       <c r="H30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N30">
         <v>4</v>
       </c>
-      <c r="O30" s="32">
+      <c r="O30" s="29">
         <v>46301</v>
       </c>
-      <c r="P30" s="32"/>
+      <c r="P30" s="29"/>
     </row>
     <row r="31" spans="7:16">
       <c r="N31">
         <v>5</v>
       </c>
-      <c r="O31" s="32">
+      <c r="O31" s="29">
         <v>46308</v>
       </c>
-      <c r="P31" s="32"/>
+      <c r="P31" s="29"/>
     </row>
     <row r="32" spans="7:16">
       <c r="H32" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="P32" s="32"/>
+        <v>87</v>
+      </c>
+      <c r="P32" s="29"/>
     </row>
     <row r="33" spans="7:16">
       <c r="H33" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="P33" s="32"/>
+        <v>88</v>
+      </c>
+      <c r="P33" s="29"/>
     </row>
     <row r="34" spans="7:16">
       <c r="H34" t="s">
-        <v>90</v>
-      </c>
-      <c r="P34" s="32"/>
+        <v>89</v>
+      </c>
+      <c r="P34" s="29"/>
     </row>
     <row r="35" spans="7:16">
-      <c r="P35" s="32"/>
+      <c r="P35" s="29"/>
     </row>
     <row r="36" spans="7:16">
       <c r="G36" t="s">
-        <v>93</v>
-      </c>
-      <c r="P36" s="32"/>
+        <v>92</v>
+      </c>
+      <c r="P36" s="29"/>
     </row>
     <row r="37" spans="7:16">
       <c r="G37" t="s">
-        <v>91</v>
-      </c>
-      <c r="P37" s="32"/>
+        <v>90</v>
+      </c>
+      <c r="P37" s="29"/>
     </row>
     <row r="38" spans="7:16">
       <c r="G38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="7:16">
-      <c r="P43" s="32"/>
+      <c r="P43" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -49041,16 +49236,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B6E0A82-03A2-4395-983D-64DB0911A0B6}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
     <col min="5" max="5" width="20.6328125" customWidth="1"/>
     <col min="6" max="7" width="8.7265625" style="2"/>
+    <col min="16" max="16" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:16">
       <c r="A1" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="12">
         <v>22000</v>
@@ -49058,13 +49255,16 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
       <c r="E1" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F1" s="12">
         <v>6500</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="P1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -49080,7 +49280,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:16">
       <c r="A3" s="11" t="s">
         <v>5</v>
       </c>
@@ -49090,21 +49290,24 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="12">
         <v>1200</v>
       </c>
-      <c r="G3" s="2">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="M3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N3">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="12">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -49114,8 +49317,19 @@
       <c r="F4" s="12">
         <v>3600</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="M4" t="s">
+        <v>97</v>
+      </c>
+      <c r="N4">
+        <f>B6</f>
+        <v>9000</v>
+      </c>
+      <c r="P4">
+        <f>N3/N4</f>
+        <v>12.222222222222221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="11"/>
       <c r="B5" s="14"/>
       <c r="C5" s="13"/>
@@ -49127,127 +49341,119 @@
         <v>390</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12">
-        <f>SUM(B1:B5)</f>
-        <v>38500</v>
+    <row r="6" spans="1:16">
+      <c r="A6" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="11">
+        <v>9000</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" s="12">
         <v>800</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:16">
       <c r="A7" s="11"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" s="12">
         <v>1200</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:16">
       <c r="A8" s="11"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" s="12">
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:16">
       <c r="A9" s="11"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="12">
         <v>13900</v>
       </c>
-      <c r="G9" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="11"/>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
       <c r="E10" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12">
         <v>500</v>
       </c>
-      <c r="G10" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="11"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="12">
         <v>500</v>
       </c>
-      <c r="G11" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="11"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" s="12">
         <v>160</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:16">
       <c r="A13" s="11"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="12">
         <v>400</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:16">
       <c r="A14" s="11"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="12">
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:16">
       <c r="A15" s="11"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -49256,43 +49462,30 @@
         <v>11</v>
       </c>
       <c r="F15" s="12">
-        <v>5000</v>
-      </c>
-      <c r="G15" s="2">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="11"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" s="12">
         <v>4000</v>
       </c>
-      <c r="G16" s="2">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="11"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="12">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="11"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -49300,9 +49493,12 @@
       <c r="E18" s="13"/>
       <c r="F18" s="12"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:6">
       <c r="A19" s="11"/>
-      <c r="B19" s="13"/>
+      <c r="B19" s="12">
+        <f>SUM(B1:B6)</f>
+        <v>51500</v>
+      </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13" t="s">
@@ -49312,7 +49508,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:6">
       <c r="A20" s="11"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -49324,97 +49520,91 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:6">
       <c r="A21" s="11"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21" s="12">
         <v>524</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:6">
       <c r="A22" s="11"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F22" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:6">
       <c r="A23" s="11"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:6">
       <c r="A24" s="11"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24" s="12">
-        <v>0</v>
-      </c>
-      <c r="G24" s="2">
         <v>380</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:6">
       <c r="A25" s="11"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:6">
       <c r="A26" s="11"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="12">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:6">
       <c r="A27" s="11"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" s="12">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2">
         <v>400</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:6">
       <c r="A28" s="11"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -49422,7 +49612,7 @@
       <c r="E28" s="13"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:6">
       <c r="A29" s="11"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -49430,7 +49620,7 @@
       <c r="E29" s="13"/>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:6">
       <c r="A30" s="11"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -49438,7 +49628,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:6">
       <c r="A31" s="11"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -49446,18 +49636,18 @@
       <c r="E31" s="13"/>
       <c r="F31" s="12"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1">
+    <row r="32" spans="1:6" ht="15" thickBot="1">
       <c r="A32" s="15"/>
       <c r="B32" s="15">
-        <f>B6-F32</f>
-        <v>-9996</v>
+        <f>B19-F32</f>
+        <v>1224</v>
       </c>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="16">
         <f>SUM(F1:F31)</f>
-        <v>48496</v>
+        <v>50276</v>
       </c>
     </row>
   </sheetData>
@@ -49476,29 +49666,29 @@
   <sheetData>
     <row r="1" spans="3:17">
       <c r="C1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="3:17">
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="3:17">
       <c r="C3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="3:17">
@@ -49506,94 +49696,94 @@
         <v>6100</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="3:17">
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2">
         <v>6100</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="3:17">
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="3:17">
       <c r="G7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="3:17">
       <c r="K8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="3:17">
       <c r="C12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="G12" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="3:17">
-      <c r="C13" s="33">
+      <c r="C13" s="30">
         <v>4</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="31">
         <v>46388</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="30">
         <v>3</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="31">
         <v>46357</v>
       </c>
     </row>
     <row r="14" spans="3:17">
-      <c r="C14" s="33">
+      <c r="C14" s="30">
         <v>17</v>
       </c>
-      <c r="D14" s="34">
+      <c r="D14" s="31">
         <v>46357</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="30">
         <v>8</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="31">
         <v>46327</v>
       </c>
     </row>
     <row r="15" spans="3:17">
-      <c r="C15" s="33">
+      <c r="C15" s="30">
         <v>8</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="31">
         <v>46327</v>
       </c>
       <c r="O15">
@@ -49607,24 +49797,24 @@
       </c>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="36"/>
-      <c r="E18" s="36" t="s">
+      <c r="B18" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="36"/>
+      <c r="C18" s="40"/>
+      <c r="E18" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="40"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" s="3">
         <v>4.8194999999999997</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="3">
         <v>2.754</v>
@@ -49636,13 +49826,13 @@
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C20" s="3">
         <v>1.573</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="3">
         <v>1.573</v>
@@ -49654,13 +49844,13 @@
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" s="3">
         <v>1.0399999999999999E-3</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="3">
         <v>1.0399999999999999E-3</v>
@@ -49670,29 +49860,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-    </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="36"/>
-      <c r="E26" s="36" t="s">
+      <c r="B26" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="36"/>
+      <c r="C26" s="40"/>
+      <c r="E26" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C27" s="3">
         <v>133</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F27" s="3">
         <v>35</v>
@@ -49704,13 +49890,13 @@
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3">
         <v>51</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F28" s="3">
         <v>0</v>
@@ -49722,13 +49908,13 @@
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="3">
         <v>25</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -49739,27 +49925,27 @@
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="38" t="s">
+      <c r="B31" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="41"/>
+      <c r="E31" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="38"/>
-      <c r="E31" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="38"/>
+      <c r="F31" s="41"/>
     </row>
     <row r="32" spans="2:8">
-      <c r="B32" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="39">
+      <c r="B32" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="33">
         <f>C19*C27</f>
         <v>640.99349999999993</v>
       </c>
-      <c r="E32" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" s="39">
+      <c r="E32" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="33">
         <f>F19*F27</f>
         <v>96.39</v>
       </c>
@@ -49769,17 +49955,17 @@
       </c>
     </row>
     <row r="33" spans="2:8">
-      <c r="B33" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="39">
+      <c r="B33" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="33">
         <f t="shared" ref="C33:C34" si="2">C20*C28</f>
         <v>80.222999999999999</v>
       </c>
-      <c r="E33" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="F33" s="39">
+      <c r="E33" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F33" s="33">
         <f t="shared" ref="F33:F34" si="3">F20*F28</f>
         <v>0</v>
       </c>
@@ -49789,17 +49975,17 @@
       </c>
     </row>
     <row r="34" spans="2:8">
-      <c r="B34" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" s="39">
+      <c r="B34" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="33">
         <f t="shared" si="2"/>
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="E34" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="F34" s="39">
+      <c r="E34" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" s="33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>

--- a/Notes/Function notes.xlsx
+++ b/Notes/Function notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Envision\Cursor\stockmanagement\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8645B6-72A1-4509-8CB2-06F2FC1CA762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0F183B-51C5-40B2-A0C5-3CFFEA60F0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="102">
   <si>
     <t>Capri</t>
   </si>
@@ -341,6 +341,12 @@
   <si>
     <t>Siyanda</t>
   </si>
+  <si>
+    <t>CM25616</t>
+  </si>
+  <si>
+    <t>ACL18603</t>
+  </si>
 </sst>
 </file>
 
@@ -605,6 +611,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -619,14 +633,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -970,14 +976,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22DBD524-30CA-4A04-AFA7-51063EBE7AE3}">
   <dimension ref="A1:Y4255"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="6" max="7" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.453125" customWidth="1"/>
-    <col min="22" max="22" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.7265625" customWidth="1"/>
+    <col min="6" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.44140625" customWidth="1"/>
+    <col min="22" max="22" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1496,7 +1502,7 @@
         <v>17000</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="18.5">
+    <row r="15" spans="1:25" ht="18">
       <c r="F15" s="6">
         <f>SUM(F2:F14)</f>
         <v>238200</v>
@@ -48153,20 +48159,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19813495-76F4-44A6-86F1-2EF0E8BEAE30}">
   <dimension ref="A1:S27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="13.90625" style="18" customWidth="1"/>
-    <col min="5" max="7" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.7265625" style="10" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" customWidth="1"/>
-    <col min="11" max="11" width="12.453125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.1796875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" style="18" customWidth="1"/>
+    <col min="5" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" style="10" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="16">
+    <row r="1" spans="1:19" ht="15.6">
       <c r="C1" s="17"/>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="39" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -48178,19 +48184,19 @@
       <c r="G1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="M1" s="38" t="s">
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="M1" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="39"/>
+      <c r="N1" s="45"/>
       <c r="R1" s="34"/>
       <c r="S1" s="34"/>
     </row>
-    <row r="2" spans="1:19" ht="16">
+    <row r="2" spans="1:19" ht="15.6">
       <c r="A2">
         <v>59480</v>
       </c>
@@ -48198,7 +48204,7 @@
         <v>46105</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="45">
+      <c r="E2" s="40">
         <v>6000</v>
       </c>
       <c r="F2" s="32"/>
@@ -48225,7 +48231,7 @@
       <c r="R2" s="35"/>
       <c r="S2" s="34"/>
     </row>
-    <row r="3" spans="1:19" ht="16">
+    <row r="3" spans="1:19" ht="15.6">
       <c r="C3" s="17">
         <v>46106</v>
       </c>
@@ -48259,12 +48265,12 @@
       <c r="R3" s="34"/>
       <c r="S3" s="34"/>
     </row>
-    <row r="4" spans="1:19" ht="16">
+    <row r="4" spans="1:19" ht="15.6">
       <c r="C4" s="17">
         <v>46113</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="45">
+      <c r="E4" s="40">
         <v>5000</v>
       </c>
       <c r="F4" s="32"/>
@@ -48287,12 +48293,12 @@
       <c r="R4" s="34"/>
       <c r="S4" s="34"/>
     </row>
-    <row r="5" spans="1:19" ht="16">
+    <row r="5" spans="1:19" ht="15.6">
       <c r="C5" s="17">
         <v>46136</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="45"/>
+      <c r="E5" s="40"/>
       <c r="F5" s="32">
         <v>42800</v>
       </c>
@@ -48321,12 +48327,12 @@
       <c r="R5" s="34"/>
       <c r="S5" s="34"/>
     </row>
-    <row r="6" spans="1:19" ht="16">
+    <row r="6" spans="1:19" ht="15.6">
       <c r="C6" s="17" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="45">
+      <c r="E6" s="40">
         <v>11000</v>
       </c>
       <c r="F6" s="32"/>
@@ -48349,12 +48355,12 @@
       <c r="R6" s="34"/>
       <c r="S6" s="34"/>
     </row>
-    <row r="7" spans="1:19" ht="16">
+    <row r="7" spans="1:19" ht="15.6">
       <c r="C7" s="17" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="45"/>
+      <c r="E7" s="40"/>
       <c r="F7" s="32">
         <v>42800</v>
       </c>
@@ -48383,12 +48389,12 @@
       <c r="R7" s="34"/>
       <c r="S7" s="34"/>
     </row>
-    <row r="8" spans="1:19" ht="16">
+    <row r="8" spans="1:19" ht="15.6">
       <c r="C8" s="17">
         <v>46176</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="45">
+      <c r="E8" s="40">
         <v>10450</v>
       </c>
       <c r="F8" s="32"/>
@@ -48411,19 +48417,25 @@
       <c r="R8" s="34"/>
       <c r="S8" s="34"/>
     </row>
-    <row r="9" spans="1:19" ht="16">
+    <row r="9" spans="1:19" ht="15.6">
       <c r="C9" s="19">
         <v>46192</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="45">
+      <c r="E9" s="40">
         <v>10000</v>
       </c>
       <c r="F9" s="32"/>
       <c r="G9" s="32"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="32"/>
+      <c r="I9" s="19">
+        <v>46265</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K9" s="32">
+        <v>18700</v>
+      </c>
       <c r="M9" s="17">
         <v>46230</v>
       </c>
@@ -48433,12 +48445,12 @@
       <c r="R9" s="34"/>
       <c r="S9" s="34"/>
     </row>
-    <row r="10" spans="1:19" ht="16">
+    <row r="10" spans="1:19" ht="15.6">
       <c r="C10" s="17">
         <v>46198</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="45">
+      <c r="E10" s="40">
         <v>10000</v>
       </c>
       <c r="F10" s="32">
@@ -48447,9 +48459,15 @@
       <c r="G10" s="32">
         <v>17500</v>
       </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="32"/>
+      <c r="I10" s="19">
+        <v>46265</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="K10" s="32">
+        <v>291.5</v>
+      </c>
       <c r="M10" s="17">
         <v>46230</v>
       </c>
@@ -48459,12 +48477,12 @@
       <c r="R10" s="34"/>
       <c r="S10" s="34"/>
     </row>
-    <row r="11" spans="1:19" ht="16">
+    <row r="11" spans="1:19" ht="15.6">
       <c r="C11" s="19">
         <v>46226</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="45">
+      <c r="E11" s="40">
         <v>10000</v>
       </c>
       <c r="F11" s="32"/>
@@ -48472,17 +48490,21 @@
       <c r="I11" s="20"/>
       <c r="J11" s="3"/>
       <c r="K11" s="32"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="3"/>
+      <c r="M11" s="17">
+        <v>46252</v>
+      </c>
+      <c r="N11" s="3">
+        <v>14000</v>
+      </c>
       <c r="R11" s="34"/>
       <c r="S11" s="34"/>
     </row>
-    <row r="12" spans="1:19" ht="16">
+    <row r="12" spans="1:19" ht="15.6">
       <c r="C12" s="17">
         <v>46230</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="45">
+      <c r="E12" s="40">
         <v>7400</v>
       </c>
       <c r="F12" s="32"/>
@@ -48495,12 +48517,12 @@
       <c r="R12" s="34"/>
       <c r="S12" s="34"/>
     </row>
-    <row r="13" spans="1:19" ht="16">
+    <row r="13" spans="1:19" ht="15.6">
       <c r="C13" s="17">
         <v>46230</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="45">
+      <c r="E13" s="40">
         <v>9800</v>
       </c>
       <c r="F13" s="32"/>
@@ -48513,12 +48535,12 @@
       <c r="R13" s="34"/>
       <c r="S13" s="34"/>
     </row>
-    <row r="14" spans="1:19" ht="16">
+    <row r="14" spans="1:19" ht="15.6">
       <c r="C14" s="17">
         <v>46231</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="45"/>
+      <c r="E14" s="40"/>
       <c r="F14" s="32">
         <v>13800</v>
       </c>
@@ -48532,12 +48554,12 @@
       <c r="N14" s="3"/>
       <c r="P14" s="2">
         <f>K27-N27</f>
-        <v>40441.5</v>
+        <v>45433</v>
       </c>
       <c r="R14" s="34"/>
       <c r="S14" s="34"/>
     </row>
-    <row r="15" spans="1:19" ht="16">
+    <row r="15" spans="1:19" ht="15.6">
       <c r="C15" s="17">
         <v>46252</v>
       </c>
@@ -48555,14 +48577,14 @@
       <c r="R15" s="34"/>
       <c r="S15" s="34"/>
     </row>
-    <row r="16" spans="1:19" ht="16">
+    <row r="16" spans="1:19" ht="15.6">
       <c r="C16" s="17">
         <v>46259</v>
       </c>
       <c r="D16" s="32">
         <v>34650</v>
       </c>
-      <c r="E16" s="45"/>
+      <c r="E16" s="40"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="I16" s="20"/>
@@ -48576,7 +48598,7 @@
     <row r="17" spans="3:14">
       <c r="C17" s="17"/>
       <c r="D17" s="3"/>
-      <c r="E17" s="46"/>
+      <c r="E17" s="41"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="20"/>
@@ -48588,7 +48610,7 @@
     <row r="18" spans="3:14">
       <c r="C18" s="17"/>
       <c r="D18" s="3"/>
-      <c r="E18" s="46"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="I18" s="20"/>
@@ -48600,7 +48622,7 @@
     <row r="19" spans="3:14">
       <c r="C19" s="17"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="47"/>
+      <c r="E19" s="42"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="20"/>
@@ -48612,7 +48634,7 @@
     <row r="20" spans="3:14">
       <c r="C20" s="17"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="46"/>
+      <c r="E20" s="41"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="20"/>
@@ -48624,7 +48646,7 @@
     <row r="21" spans="3:14">
       <c r="C21" s="17"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="46"/>
+      <c r="E21" s="41"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="20"/>
@@ -48636,7 +48658,7 @@
     <row r="22" spans="3:14">
       <c r="C22" s="17"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="46"/>
+      <c r="E22" s="41"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="20"/>
@@ -48648,7 +48670,7 @@
     <row r="23" spans="3:14">
       <c r="C23" s="17"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="46"/>
+      <c r="E23" s="41"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="20"/>
@@ -48660,7 +48682,7 @@
     <row r="24" spans="3:14">
       <c r="C24" s="17"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="46"/>
+      <c r="E24" s="41"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="20"/>
@@ -48672,7 +48694,7 @@
     <row r="25" spans="3:14">
       <c r="C25" s="17"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="46"/>
+      <c r="E25" s="41"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="20"/>
@@ -48684,7 +48706,7 @@
     <row r="26" spans="3:14">
       <c r="C26" s="17"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="46"/>
+      <c r="E26" s="41"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="I26" s="20"/>
@@ -48714,13 +48736,13 @@
         <f>SUM(D27:G27)</f>
         <v>373800</v>
       </c>
-      <c r="K27" s="43">
+      <c r="K27" s="38">
         <f>SUM(K2:K13)</f>
-        <v>120091.5</v>
-      </c>
-      <c r="N27" s="42">
+        <v>139083</v>
+      </c>
+      <c r="N27" s="37">
         <f>SUM(N2:N13)</f>
-        <v>79650</v>
+        <v>93650</v>
       </c>
     </row>
   </sheetData>
@@ -48736,14 +48758,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4750D6-39CA-4555-B7BD-12504A33D1C5}">
   <dimension ref="B1:P43"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="7" max="7" width="37" customWidth="1"/>
     <col min="8" max="8" width="61" customWidth="1"/>
-    <col min="9" max="9" width="15.81640625" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" customWidth="1"/>
-    <col min="15" max="15" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="15.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15">
@@ -49002,7 +49024,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
     </row>
-    <row r="16" spans="2:15" ht="16">
+    <row r="16" spans="2:15" ht="15.6">
       <c r="G16" s="27" t="s">
         <v>51</v>
       </c>
@@ -49015,7 +49037,7 @@
       <c r="J16" s="28"/>
       <c r="K16" s="25"/>
     </row>
-    <row r="17" spans="7:16" ht="16">
+    <row r="17" spans="7:16" ht="15.6">
       <c r="G17" s="27" t="s">
         <v>53</v>
       </c>
@@ -49028,14 +49050,14 @@
       <c r="J17" s="25"/>
       <c r="K17" s="25"/>
     </row>
-    <row r="18" spans="7:16" ht="16">
+    <row r="18" spans="7:16" ht="15.6">
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
       <c r="I18" s="25"/>
       <c r="J18" s="25"/>
       <c r="K18" s="25"/>
     </row>
-    <row r="19" spans="7:16" ht="16">
+    <row r="19" spans="7:16" ht="15.6">
       <c r="G19" s="27" t="s">
         <v>52</v>
       </c>
@@ -49052,7 +49074,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="7:16" ht="16">
+    <row r="20" spans="7:16" ht="15.6">
       <c r="G20" s="27" t="s">
         <v>54</v>
       </c>
@@ -49237,12 +49259,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B6E0A82-03A2-4395-983D-64DB0911A0B6}">
   <dimension ref="A1:P32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" customWidth="1"/>
-    <col min="5" max="5" width="20.6328125" customWidth="1"/>
-    <col min="6" max="7" width="8.7265625" style="2"/>
-    <col min="16" max="16" width="13.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="7" width="8.77734375" style="2"/>
+    <col min="16" max="16" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -49658,10 +49680,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C21136-C2F8-41B1-9BF0-1E816375C2F6}">
   <dimension ref="B1:Q34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="7" max="7" width="11.6328125" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:17">
@@ -49797,14 +49819,14 @@
       </c>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="E18" s="40" t="s">
+      <c r="C18" s="46"/>
+      <c r="E18" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="40"/>
+      <c r="F18" s="46"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="3" t="s">
@@ -49861,14 +49883,14 @@
       </c>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="E26" s="40" t="s">
+      <c r="C26" s="46"/>
+      <c r="E26" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="40"/>
+      <c r="F26" s="46"/>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="3" t="s">
@@ -49925,14 +49947,14 @@
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="E31" s="41" t="s">
+      <c r="C31" s="47"/>
+      <c r="E31" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="41"/>
+      <c r="F31" s="47"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="33" t="s">

--- a/Notes/Function notes.xlsx
+++ b/Notes/Function notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Envision\Cursor\stockmanagement\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0F183B-51C5-40B2-A0C5-3CFFEA60F0F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D46518-131B-49C3-A9B8-CEF1C6DD3187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Inklomste vir Belasting 2025" sheetId="1" r:id="rId1"/>
@@ -611,7 +611,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -634,6 +633,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -48167,12 +48167,12 @@
     <col min="10" max="10" width="15.21875" customWidth="1"/>
     <col min="11" max="11" width="12.44140625" style="2" customWidth="1"/>
     <col min="13" max="13" width="16.21875" style="10" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="15.6">
       <c r="C1" s="17"/>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -48184,15 +48184,15 @@
       <c r="G1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="43" t="s">
+      <c r="I1" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="M1" s="44" t="s">
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="M1" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="45"/>
+      <c r="N1" s="44"/>
       <c r="R1" s="34"/>
       <c r="S1" s="34"/>
     </row>
@@ -48204,7 +48204,7 @@
         <v>46105</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="40">
+      <c r="E2" s="39">
         <v>6000</v>
       </c>
       <c r="F2" s="32"/>
@@ -48270,7 +48270,7 @@
         <v>46113</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="40">
+      <c r="E4" s="39">
         <v>5000</v>
       </c>
       <c r="F4" s="32"/>
@@ -48298,7 +48298,7 @@
         <v>46136</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="40"/>
+      <c r="E5" s="39"/>
       <c r="F5" s="32">
         <v>42800</v>
       </c>
@@ -48332,7 +48332,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="40">
+      <c r="E6" s="39">
         <v>11000</v>
       </c>
       <c r="F6" s="32"/>
@@ -48360,7 +48360,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="40"/>
+      <c r="E7" s="39"/>
       <c r="F7" s="32">
         <v>42800</v>
       </c>
@@ -48394,7 +48394,7 @@
         <v>46176</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="40">
+      <c r="E8" s="39">
         <v>10450</v>
       </c>
       <c r="F8" s="32"/>
@@ -48422,7 +48422,7 @@
         <v>46192</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="40">
+      <c r="E9" s="39">
         <v>10000</v>
       </c>
       <c r="F9" s="32"/>
@@ -48450,7 +48450,7 @@
         <v>46198</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="40">
+      <c r="E10" s="39">
         <v>10000</v>
       </c>
       <c r="F10" s="32">
@@ -48482,7 +48482,7 @@
         <v>46226</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="40">
+      <c r="E11" s="39">
         <v>10000</v>
       </c>
       <c r="F11" s="32"/>
@@ -48493,7 +48493,7 @@
       <c r="M11" s="17">
         <v>46252</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="32">
         <v>14000</v>
       </c>
       <c r="R11" s="34"/>
@@ -48504,7 +48504,7 @@
         <v>46230</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>7400</v>
       </c>
       <c r="F12" s="32"/>
@@ -48512,8 +48512,12 @@
       <c r="I12" s="20"/>
       <c r="J12" s="3"/>
       <c r="K12" s="32"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="32"/>
+      <c r="M12" s="17">
+        <v>46282</v>
+      </c>
+      <c r="N12" s="32">
+        <v>7450</v>
+      </c>
       <c r="R12" s="34"/>
       <c r="S12" s="34"/>
     </row>
@@ -48522,7 +48526,7 @@
         <v>46230</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="40">
+      <c r="E13" s="39">
         <v>9800</v>
       </c>
       <c r="F13" s="32"/>
@@ -48540,7 +48544,7 @@
         <v>46231</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="40"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="32">
         <v>13800</v>
       </c>
@@ -48551,10 +48555,10 @@
       <c r="J14" s="3"/>
       <c r="K14" s="5"/>
       <c r="M14" s="17"/>
-      <c r="N14" s="3"/>
+      <c r="N14" s="32"/>
       <c r="P14" s="2">
         <f>K27-N27</f>
-        <v>45433</v>
+        <v>37983</v>
       </c>
       <c r="R14" s="34"/>
       <c r="S14" s="34"/>
@@ -48573,7 +48577,7 @@
       <c r="J15" s="3"/>
       <c r="K15" s="5"/>
       <c r="M15" s="20"/>
-      <c r="N15" s="3"/>
+      <c r="N15" s="32"/>
       <c r="R15" s="34"/>
       <c r="S15" s="34"/>
     </row>
@@ -48584,136 +48588,146 @@
       <c r="D16" s="32">
         <v>34650</v>
       </c>
-      <c r="E16" s="40"/>
+      <c r="E16" s="39"/>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
       <c r="I16" s="20"/>
       <c r="J16" s="3"/>
       <c r="K16" s="5"/>
       <c r="M16" s="20"/>
-      <c r="N16" s="3"/>
+      <c r="N16" s="32"/>
       <c r="R16" s="34"/>
       <c r="S16" s="34"/>
     </row>
     <row r="17" spans="3:14">
-      <c r="C17" s="17"/>
+      <c r="C17" s="17">
+        <v>46282</v>
+      </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="41"/>
+      <c r="E17" s="47">
+        <v>7450</v>
+      </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="20"/>
       <c r="J17" s="3"/>
       <c r="K17" s="5"/>
       <c r="M17" s="20"/>
-      <c r="N17" s="3"/>
+      <c r="N17" s="32"/>
     </row>
     <row r="18" spans="3:14">
-      <c r="C18" s="17"/>
+      <c r="C18" s="17">
+        <v>46287</v>
+      </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>8000</v>
+      </c>
       <c r="I18" s="20"/>
       <c r="J18" s="3"/>
       <c r="K18" s="5"/>
       <c r="M18" s="20"/>
-      <c r="N18" s="3"/>
+      <c r="N18" s="32"/>
     </row>
     <row r="19" spans="3:14">
       <c r="C19" s="17"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="42"/>
+      <c r="E19" s="41"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="20"/>
       <c r="J19" s="3"/>
       <c r="K19" s="5"/>
       <c r="M19" s="20"/>
-      <c r="N19" s="3"/>
+      <c r="N19" s="32"/>
     </row>
     <row r="20" spans="3:14">
       <c r="C20" s="17"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="41"/>
+      <c r="E20" s="40"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="I20" s="20"/>
       <c r="J20" s="3"/>
       <c r="K20" s="5"/>
       <c r="M20" s="20"/>
-      <c r="N20" s="3"/>
+      <c r="N20" s="32"/>
     </row>
     <row r="21" spans="3:14">
       <c r="C21" s="17"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="41"/>
+      <c r="E21" s="40"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="20"/>
       <c r="J21" s="3"/>
       <c r="K21" s="5"/>
       <c r="M21" s="20"/>
-      <c r="N21" s="3"/>
+      <c r="N21" s="32"/>
     </row>
     <row r="22" spans="3:14">
       <c r="C22" s="17"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="41"/>
+      <c r="E22" s="40"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="20"/>
       <c r="J22" s="3"/>
       <c r="K22" s="5"/>
       <c r="M22" s="20"/>
-      <c r="N22" s="3"/>
+      <c r="N22" s="32"/>
     </row>
     <row r="23" spans="3:14">
       <c r="C23" s="17"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="41"/>
+      <c r="E23" s="40"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="I23" s="20"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
       <c r="M23" s="20"/>
-      <c r="N23" s="3"/>
+      <c r="N23" s="32"/>
     </row>
     <row r="24" spans="3:14">
       <c r="C24" s="17"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="41"/>
+      <c r="E24" s="40"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="I24" s="20"/>
       <c r="J24" s="3"/>
       <c r="K24" s="5"/>
       <c r="M24" s="20"/>
-      <c r="N24" s="3"/>
+      <c r="N24" s="32"/>
     </row>
     <row r="25" spans="3:14">
       <c r="C25" s="17"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="41"/>
+      <c r="E25" s="40"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="I25" s="20"/>
       <c r="J25" s="3"/>
       <c r="K25" s="5"/>
       <c r="M25" s="20"/>
-      <c r="N25" s="3"/>
+      <c r="N25" s="32"/>
     </row>
     <row r="26" spans="3:14">
       <c r="C26" s="17"/>
       <c r="D26" s="3"/>
-      <c r="E26" s="41"/>
+      <c r="E26" s="40"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="I26" s="20"/>
       <c r="J26" s="3"/>
       <c r="K26" s="5"/>
       <c r="M26" s="20"/>
-      <c r="N26" s="3"/>
+      <c r="N26" s="32"/>
     </row>
     <row r="27" spans="3:14">
       <c r="D27">
@@ -48721,8 +48735,8 @@
         <v>34650</v>
       </c>
       <c r="E27" s="21">
-        <f>SUM(E2:E16)</f>
-        <v>93650</v>
+        <f>SUM(E2:E17)</f>
+        <v>101100</v>
       </c>
       <c r="F27" s="21">
         <f>SUM(F2:F16)</f>
@@ -48734,15 +48748,15 @@
       </c>
       <c r="H27" s="21">
         <f>SUM(D27:G27)</f>
-        <v>373800</v>
-      </c>
-      <c r="K27" s="38">
+        <v>381250</v>
+      </c>
+      <c r="K27" s="37">
         <f>SUM(K2:K13)</f>
         <v>139083</v>
       </c>
       <c r="N27" s="37">
         <f>SUM(N2:N13)</f>
-        <v>93650</v>
+        <v>101100</v>
       </c>
     </row>
   </sheetData>
@@ -49819,14 +49833,14 @@
       </c>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="46"/>
-      <c r="E18" s="46" t="s">
+      <c r="C18" s="45"/>
+      <c r="E18" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="46"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="3" t="s">
@@ -49883,14 +49897,14 @@
       </c>
     </row>
     <row r="26" spans="2:8">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="46"/>
-      <c r="E26" s="46" t="s">
+      <c r="C26" s="45"/>
+      <c r="E26" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="46"/>
+      <c r="F26" s="45"/>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="3" t="s">
@@ -49947,14 +49961,14 @@
       </c>
     </row>
     <row r="31" spans="2:8">
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="E31" s="47" t="s">
+      <c r="C31" s="46"/>
+      <c r="E31" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="F31" s="47"/>
+      <c r="F31" s="46"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="33" t="s">

--- a/Notes/Function notes.xlsx
+++ b/Notes/Function notes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Envision\Cursor\stockmanagement\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D46518-131B-49C3-A9B8-CEF1C6DD3187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FC6E26-4297-42D6-82A6-74AE58FF23FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="104">
   <si>
     <t>Capri</t>
   </si>
@@ -347,6 +347,12 @@
   <si>
     <t>ACL18603</t>
   </si>
+  <si>
+    <t>CM25617</t>
+  </si>
+  <si>
+    <t>ACL18604</t>
+  </si>
 </sst>
 </file>
 
@@ -557,7 +563,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -633,7 +639,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -48162,7 +48167,8 @@
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="13.88671875" style="18" customWidth="1"/>
-    <col min="5" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.77734375" style="10" customWidth="1"/>
     <col min="10" max="10" width="15.21875" customWidth="1"/>
     <col min="11" max="11" width="12.44140625" style="2" customWidth="1"/>
@@ -48487,9 +48493,15 @@
       </c>
       <c r="F11" s="32"/>
       <c r="G11" s="32"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="32"/>
+      <c r="I11" s="19">
+        <v>46295</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="32">
+        <v>18700</v>
+      </c>
       <c r="M11" s="17">
         <v>46252</v>
       </c>
@@ -48509,9 +48521,15 @@
       </c>
       <c r="F12" s="32"/>
       <c r="G12" s="32"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="32"/>
+      <c r="I12" s="19">
+        <v>46295</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K12" s="32">
+        <v>291.5</v>
+      </c>
       <c r="M12" s="17">
         <v>46282</v>
       </c>
@@ -48534,8 +48552,12 @@
       <c r="I13" s="20"/>
       <c r="J13" s="3"/>
       <c r="K13" s="32"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="32"/>
+      <c r="M13" s="17">
+        <v>46295</v>
+      </c>
+      <c r="N13" s="32">
+        <v>7000</v>
+      </c>
       <c r="R13" s="34"/>
       <c r="S13" s="34"/>
     </row>
@@ -48558,7 +48580,7 @@
       <c r="N14" s="32"/>
       <c r="P14" s="2">
         <f>K27-N27</f>
-        <v>37983</v>
+        <v>49974.5</v>
       </c>
       <c r="R14" s="34"/>
       <c r="S14" s="34"/>
@@ -48604,7 +48626,7 @@
         <v>46282</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="47">
+      <c r="E17" s="32">
         <v>7450</v>
       </c>
       <c r="F17" s="3"/>
@@ -48634,9 +48656,13 @@
       <c r="N18" s="32"/>
     </row>
     <row r="19" spans="3:14">
-      <c r="C19" s="17"/>
+      <c r="C19" s="17">
+        <v>46295</v>
+      </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="41"/>
+      <c r="E19" s="41">
+        <v>7000</v>
+      </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="I19" s="20"/>
@@ -48752,11 +48778,11 @@
       </c>
       <c r="K27" s="37">
         <f>SUM(K2:K13)</f>
-        <v>139083</v>
+        <v>158074.5</v>
       </c>
       <c r="N27" s="37">
         <f>SUM(N2:N13)</f>
-        <v>101100</v>
+        <v>108100</v>
       </c>
     </row>
   </sheetData>
@@ -49278,6 +49304,7 @@
     <col min="1" max="1" width="10.33203125" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" customWidth="1"/>
     <col min="6" max="7" width="8.77734375" style="2"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
     <col min="16" max="16" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -49296,6 +49323,9 @@
       <c r="F1" s="12">
         <v>6500</v>
       </c>
+      <c r="H1" s="12">
+        <v>6500</v>
+      </c>
       <c r="P1" t="s">
         <v>98</v>
       </c>
@@ -49313,8 +49343,9 @@
         <v>14</v>
       </c>
       <c r="F2" s="12">
-        <v>1000</v>
-      </c>
+        <v>1009</v>
+      </c>
+      <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="11" t="s">
@@ -49331,6 +49362,9 @@
       <c r="F3" s="12">
         <v>1200</v>
       </c>
+      <c r="H3" s="12">
+        <v>1200</v>
+      </c>
       <c r="M3" t="s">
         <v>95</v>
       </c>
@@ -49353,16 +49387,19 @@
       <c r="F4" s="12">
         <v>3600</v>
       </c>
+      <c r="J4" s="12">
+        <v>3600</v>
+      </c>
       <c r="M4" t="s">
         <v>97</v>
       </c>
       <c r="N4">
         <f>B6</f>
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="P4">
         <f>N3/N4</f>
-        <v>12.222222222222221</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -49376,13 +49413,16 @@
       <c r="F5" s="12">
         <v>390</v>
       </c>
+      <c r="H5" s="12">
+        <v>390</v>
+      </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="11" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="11">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -49390,6 +49430,9 @@
         <v>34</v>
       </c>
       <c r="F6" s="12">
+        <v>800</v>
+      </c>
+      <c r="H6" s="12">
         <v>800</v>
       </c>
     </row>
@@ -49404,6 +49447,9 @@
       <c r="F7" s="12">
         <v>1200</v>
       </c>
+      <c r="H7" s="12">
+        <v>1200</v>
+      </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="11"/>
@@ -49416,6 +49462,9 @@
       <c r="F8" s="12">
         <v>200</v>
       </c>
+      <c r="J8" s="12">
+        <v>200</v>
+      </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="11"/>
@@ -49428,6 +49477,9 @@
       <c r="F9" s="12">
         <v>13900</v>
       </c>
+      <c r="H9" s="12">
+        <v>13900</v>
+      </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="11"/>
@@ -49440,6 +49492,9 @@
       <c r="F10" s="12">
         <v>500</v>
       </c>
+      <c r="J10" s="12">
+        <v>500</v>
+      </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="11"/>
@@ -49450,7 +49505,10 @@
         <v>36</v>
       </c>
       <c r="F11" s="12">
-        <v>500</v>
+        <v>1500</v>
+      </c>
+      <c r="J11" s="12">
+        <v>1500</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -49464,6 +49522,9 @@
       <c r="F12" s="12">
         <v>160</v>
       </c>
+      <c r="H12" s="12">
+        <v>160</v>
+      </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="11"/>
@@ -49476,6 +49537,9 @@
       <c r="F13" s="12">
         <v>400</v>
       </c>
+      <c r="J13" s="12">
+        <v>400</v>
+      </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="11"/>
@@ -49488,6 +49552,9 @@
       <c r="F14" s="12">
         <v>622</v>
       </c>
+      <c r="J14" s="12">
+        <v>622</v>
+      </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="11"/>
@@ -49500,6 +49567,7 @@
       <c r="F15" s="12">
         <v>6000</v>
       </c>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="11"/>
@@ -49512,28 +49580,31 @@
       <c r="F16" s="12">
         <v>4000</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="11"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
       <c r="F17" s="12"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="11"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
       <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="11"/>
       <c r="B19" s="12">
         <f>SUM(B1:B6)</f>
-        <v>51500</v>
+        <v>52500</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -49543,8 +49614,9 @@
       <c r="F19" s="12">
         <v>5000</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="11"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -49555,8 +49627,11 @@
       <c r="F20" s="12">
         <v>3000</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="J20" s="12">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="11"/>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -49567,8 +49642,11 @@
       <c r="F21" s="12">
         <v>524</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="H21" s="12">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="11"/>
       <c r="B22" s="13"/>
       <c r="C22" s="13"/>
@@ -49579,8 +49657,11 @@
       <c r="F22" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="H22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="11"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -49591,8 +49672,11 @@
       <c r="F23" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="H23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="11"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -49603,8 +49687,9 @@
       <c r="F24" s="12">
         <v>380</v>
       </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="11"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -49615,8 +49700,11 @@
       <c r="F25" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="H25" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="11"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -49627,8 +49715,11 @@
       <c r="F26" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="H26" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="11"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -49639,51 +49730,66 @@
       <c r="F27" s="12">
         <v>400</v>
       </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="H27" s="12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="11"/>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="11"/>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
       <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="11"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="11"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1">
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" thickBot="1">
       <c r="A32" s="15"/>
       <c r="B32" s="15">
         <f>B19-F32</f>
-        <v>1224</v>
+        <v>1215</v>
       </c>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="16">
         <f>SUM(F1:F31)</f>
-        <v>50276</v>
+        <v>51285</v>
+      </c>
+      <c r="H32" s="2">
+        <f>SUM(H1:H31)</f>
+        <v>25074</v>
+      </c>
+      <c r="J32">
+        <f>SUM(J1:J31)</f>
+        <v>9822</v>
       </c>
     </row>
   </sheetData>

--- a/Notes/Function notes.xlsx
+++ b/Notes/Function notes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Envision\Cursor\stockmanagement\Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21FC6E26-4297-42D6-82A6-74AE58FF23FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FF48F7B-DA22-485C-8378-1DB08360CDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9CBB7EE9-BC98-484E-AF7B-064CC0EC69BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Inklomste vir Belasting 2025" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="111">
   <si>
     <t>Capri</t>
   </si>
@@ -353,6 +353,114 @@
   <si>
     <t>ACL18604</t>
   </si>
+  <si>
+    <r>
+      <t>get_stock_to_sell_1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Add-knoppie op orders-out</t>
+  </si>
+  <si>
+    <r>
+      <t>On Orders Out, when </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>editMode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> is false, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> runs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>handleAdd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, which calls </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>pi_order_out</t>
+    </r>
+  </si>
+  <si>
+    <t>pr_orders_out_by_customer</t>
+  </si>
+  <si>
+    <t>Grid onder-aan orders-out</t>
+  </si>
+  <si>
+    <r>
+      <t>pr_order_booking_out</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>Grid in Items seksie</t>
+  </si>
 </sst>
 </file>
 
@@ -361,7 +469,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +550,30 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Geist"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="7">
@@ -563,7 +695,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -639,6 +771,11 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -48797,7 +48934,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4750D6-39CA-4555-B7BD-12504A33D1C5}">
-  <dimension ref="B1:P43"/>
+  <dimension ref="B1:P44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="7" max="7" width="37" customWidth="1"/>
@@ -49133,72 +49270,40 @@
       <c r="P20" s="29"/>
     </row>
     <row r="21" spans="7:16">
-      <c r="O21" s="29">
-        <v>46238</v>
-      </c>
+      <c r="O21" s="29"/>
       <c r="P21" s="29"/>
     </row>
     <row r="22" spans="7:16">
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22" s="29">
-        <v>46245</v>
-      </c>
+      <c r="O22" s="29"/>
       <c r="P22" s="29"/>
     </row>
     <row r="23" spans="7:16">
-      <c r="N23">
-        <v>2</v>
-      </c>
-      <c r="O23" s="29">
-        <v>46252</v>
-      </c>
+      <c r="O23" s="29"/>
       <c r="P23" s="29"/>
     </row>
     <row r="24" spans="7:16">
       <c r="G24" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="N24">
-        <v>3</v>
-      </c>
-      <c r="O24" s="29">
-        <v>46259</v>
-      </c>
+      <c r="O24" s="29"/>
       <c r="P24" s="29"/>
     </row>
     <row r="25" spans="7:16">
       <c r="G25" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="N25">
-        <v>4</v>
-      </c>
-      <c r="O25" s="29">
-        <v>46266</v>
-      </c>
+      <c r="O25" s="29"/>
       <c r="P25" s="29"/>
     </row>
     <row r="26" spans="7:16">
       <c r="G26" t="s">
         <v>63</v>
       </c>
-      <c r="N26">
-        <v>5</v>
-      </c>
-      <c r="O26" s="29">
-        <v>46273</v>
-      </c>
+      <c r="O26" s="29"/>
       <c r="P26" s="29"/>
     </row>
     <row r="27" spans="7:16">
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27" s="29">
-        <v>46280</v>
-      </c>
+      <c r="O27" s="29"/>
       <c r="P27" s="29"/>
     </row>
     <row r="28" spans="7:16">
@@ -49208,45 +49313,25 @@
       <c r="H28" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="N28">
-        <v>2</v>
-      </c>
-      <c r="O28" s="29">
-        <v>46287</v>
-      </c>
+      <c r="O28" s="29"/>
       <c r="P28" s="29"/>
     </row>
     <row r="29" spans="7:16">
       <c r="H29" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="N29">
-        <v>3</v>
-      </c>
-      <c r="O29" s="29">
-        <v>46294</v>
-      </c>
+      <c r="O29" s="29"/>
       <c r="P29" s="29"/>
     </row>
     <row r="30" spans="7:16">
       <c r="H30" t="s">
         <v>63</v>
       </c>
-      <c r="N30">
-        <v>4</v>
-      </c>
-      <c r="O30" s="29">
-        <v>46301</v>
-      </c>
+      <c r="O30" s="29"/>
       <c r="P30" s="29"/>
     </row>
     <row r="31" spans="7:16">
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31" s="29">
-        <v>46308</v>
-      </c>
+      <c r="O31" s="29"/>
       <c r="P31" s="29"/>
     </row>
     <row r="32" spans="7:16">
@@ -49287,10 +49372,41 @@
         <v>91</v>
       </c>
     </row>
+    <row r="41" spans="7:16">
+      <c r="G41" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="H41" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="7:16">
+      <c r="G42" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="H42" s="48"/>
+    </row>
     <row r="43" spans="7:16">
+      <c r="G43" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="H43" t="s">
+        <v>108</v>
+      </c>
       <c r="P43" s="29"/>
     </row>
+    <row r="44" spans="7:16">
+      <c r="G44" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="H44" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G42:H42"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -49413,9 +49529,7 @@
       <c r="F5" s="12">
         <v>390</v>
       </c>
-      <c r="H5" s="12">
-        <v>390</v>
-      </c>
+      <c r="H5" s="12"/>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="11" t="s">
@@ -49432,9 +49546,7 @@
       <c r="F6" s="12">
         <v>800</v>
       </c>
-      <c r="H6" s="12">
-        <v>800</v>
-      </c>
+      <c r="H6" s="12"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="11"/>
@@ -49447,9 +49559,7 @@
       <c r="F7" s="12">
         <v>1200</v>
       </c>
-      <c r="H7" s="12">
-        <v>1200</v>
-      </c>
+      <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="11"/>
@@ -49490,7 +49600,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="12">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="J10" s="12">
         <v>500</v>
@@ -49774,18 +49884,18 @@
       <c r="A32" s="15"/>
       <c r="B32" s="15">
         <f>B19-F32</f>
-        <v>1215</v>
+        <v>215</v>
       </c>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
       <c r="F32" s="16">
         <f>SUM(F1:F31)</f>
-        <v>51285</v>
+        <v>52285</v>
       </c>
       <c r="H32" s="2">
         <f>SUM(H1:H31)</f>
-        <v>25074</v>
+        <v>22684</v>
       </c>
       <c r="J32">
         <f>SUM(J1:J31)</f>
